--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260818.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>5,792,000</t>
+          <t>6,022,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>9,937,000</t>
+          <t>10,306,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.61%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,281,000</t>
+          <t>21,610,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -677,144 +677,144 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6,021,000</t>
+          <t>6,066,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>47,420,000</t>
+          <t>3,875,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>35,599,000</t>
+          <t>47,874,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>9,871,000</t>
+          <t>35,599,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>20,234,000</t>
+          <t>3,854,665,141</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,829,000</t>
+          <t>9,871,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>3,748,441,033</t>
+          <t>20,426,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -836,359 +836,359 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>202609WTX</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>115/09台股期貨</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>6,624,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>202609WTX</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>115/09台股期貨</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>26,121,000</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.51%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>34,668,000</t>
+          <t>26,121,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>31,215,000</t>
+          <t>34,668,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>9,588,000</t>
+          <t>31,753,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>6,538,000</t>
+          <t>22,764,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>4,161,000</t>
+          <t>9,588,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2,845,000</t>
+          <t>36,256,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>34,072,000</t>
+          <t>4,161,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>20,776,000</t>
+          <t>2,845,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,187,000</t>
+          <t>4,234,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,548,000</t>
+          <t>2,187,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>3,897,000</t>
+          <t>9,548,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>15,188,000</t>
+          <t>543,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,521,000</t>
+          <t>15,188,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>543,000</t>
+          <t>18,002,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,647,281,747</t>
+          <t>2,580,401,747</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -1276,73 +1276,73 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,023,000</t>
+          <t>4,984,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,652,000</t>
+          <t>6,077,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>4,928,000</t>
+          <t>9,652,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1359,78 +1359,78 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>14,245,000</t>
+          <t>14,372,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>23,917,004</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>16,642,000</t>
+          <t>24,122,004</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>13,914,000</t>
+          <t>7,883,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>23,400,000</t>
+          <t>23,651,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,61 +1459,61 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,529,000</t>
+          <t>16,642,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>8,785,000</t>
+          <t>14,037,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,285,000</t>
+          <t>9,699,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>9,042,000</t>
+          <t>8,984,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>2,113,000</t>
+          <t>2,298,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1628,51 +1628,51 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>47,579,000</t>
+          <t>50,097,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>49,379,000</t>
+          <t>47,991,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>6,399,000</t>
+          <t>6,467,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-151,864,896</t>
+          <t>-268,134,075</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.19%</t>
         </is>
       </c>
     </row>
